--- a/currentbuild/StructureDefinition-no-basis-encounter-auditevent.xlsx
+++ b/currentbuild/StructureDefinition-no-basis-encounter-auditevent.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3072" uniqueCount="522">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3071" uniqueCount="523">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.8.3</t>
+    <t>0.9.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-15T09:00:42+00:00</t>
+    <t>2024-03-17T09:59:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -743,6 +743,9 @@
   </si>
   <si>
     <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
+  </si>
+  <si>
+    <t>urn:no-basis-auditevent/ValueSet/no-basis-encounter-auditevent-servicetype</t>
   </si>
   <si>
     <t>CodeableConcept.coding</t>
@@ -1949,7 +1952,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="74.65625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="56.25390625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="71.91796875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
@@ -5324,13 +5327,11 @@
         <v>78</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y30" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="Y30" s="2"/>
       <c r="Z30" t="s" s="2">
-        <v>78</v>
+        <v>235</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>78</v>
@@ -5348,7 +5349,7 @@
         <v>78</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>76</v>
@@ -5366,21 +5367,21 @@
         <v>78</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5489,10 +5490,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5603,10 +5604,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5632,16 +5633,16 @@
         <v>100</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>78</v>
@@ -5690,7 +5691,7 @@
         <v>78</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>76</v>
@@ -5708,21 +5709,21 @@
         <v>78</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5748,13 +5749,13 @@
         <v>169</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -5804,7 +5805,7 @@
         <v>78</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>76</v>
@@ -5822,21 +5823,21 @@
         <v>78</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5862,14 +5863,14 @@
         <v>106</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>78</v>
@@ -5918,7 +5919,7 @@
         <v>78</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>76</v>
@@ -5936,21 +5937,21 @@
         <v>78</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5976,14 +5977,14 @@
         <v>169</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>78</v>
@@ -6032,7 +6033,7 @@
         <v>78</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>76</v>
@@ -6050,21 +6051,21 @@
         <v>78</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6087,19 +6088,19 @@
         <v>87</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>78</v>
@@ -6148,7 +6149,7 @@
         <v>78</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>76</v>
@@ -6166,21 +6167,21 @@
         <v>78</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6206,16 +6207,16 @@
         <v>169</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>78</v>
@@ -6264,7 +6265,7 @@
         <v>78</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>76</v>
@@ -6282,21 +6283,21 @@
         <v>78</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6322,10 +6323,10 @@
         <v>209</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6355,10 +6356,10 @@
         <v>213</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>78</v>
@@ -6376,7 +6377,7 @@
         <v>78</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>76</v>
@@ -6394,25 +6395,25 @@
         <v>78</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -6431,16 +6432,16 @@
         <v>87</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6490,7 +6491,7 @@
         <v>78</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>76</v>
@@ -6505,24 +6506,24 @@
         <v>98</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6545,13 +6546,13 @@
         <v>87</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6602,7 +6603,7 @@
         <v>78</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>76</v>
@@ -6617,28 +6618,28 @@
         <v>98</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>167</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -6657,13 +6658,13 @@
         <v>78</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6714,7 +6715,7 @@
         <v>78</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>76</v>
@@ -6729,10 +6730,10 @@
         <v>98</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>78</v>
@@ -6743,10 +6744,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6772,10 +6773,10 @@
         <v>163</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6826,7 +6827,7 @@
         <v>78</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>76</v>
@@ -6841,24 +6842,24 @@
         <v>98</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6967,10 +6968,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7081,10 +7082,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7197,10 +7198,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7226,13 +7227,13 @@
         <v>209</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7261,10 +7262,10 @@
         <v>190</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>78</v>
@@ -7282,7 +7283,7 @@
         <v>78</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>76</v>
@@ -7297,24 +7298,24 @@
         <v>98</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7340,10 +7341,10 @@
         <v>183</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7394,7 +7395,7 @@
         <v>78</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>76</v>
@@ -7412,21 +7413,21 @@
         <v>78</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7449,13 +7450,13 @@
         <v>87</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7506,7 +7507,7 @@
         <v>78</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>76</v>
@@ -7521,24 +7522,24 @@
         <v>98</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7561,13 +7562,13 @@
         <v>87</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7618,7 +7619,7 @@
         <v>78</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>76</v>
@@ -7633,24 +7634,24 @@
         <v>98</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7676,13 +7677,13 @@
         <v>183</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -7732,7 +7733,7 @@
         <v>78</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>76</v>
@@ -7747,24 +7748,24 @@
         <v>98</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7787,16 +7788,16 @@
         <v>78</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -7846,7 +7847,7 @@
         <v>78</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>76</v>
@@ -7861,28 +7862,28 @@
         <v>98</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -7904,13 +7905,13 @@
         <v>209</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -7939,10 +7940,10 @@
         <v>110</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>78</v>
@@ -7960,7 +7961,7 @@
         <v>78</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>76</v>
@@ -7975,28 +7976,28 @@
         <v>98</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -8015,16 +8016,16 @@
         <v>87</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8074,7 +8075,7 @@
         <v>78</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>76</v>
@@ -8089,24 +8090,24 @@
         <v>98</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8132,10 +8133,10 @@
         <v>163</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -8186,7 +8187,7 @@
         <v>78</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>76</v>
@@ -8204,7 +8205,7 @@
         <v>78</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>78</v>
@@ -8215,10 +8216,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8327,10 +8328,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8441,10 +8442,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8557,14 +8558,14 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -8583,16 +8584,16 @@
         <v>87</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -8642,7 +8643,7 @@
         <v>78</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>86</v>
@@ -8657,24 +8658,24 @@
         <v>98</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8700,10 +8701,10 @@
         <v>209</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -8733,10 +8734,10 @@
         <v>110</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>78</v>
@@ -8754,7 +8755,7 @@
         <v>78</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>76</v>
@@ -8783,10 +8784,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8809,13 +8810,13 @@
         <v>78</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -8866,7 +8867,7 @@
         <v>78</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>76</v>
@@ -8884,7 +8885,7 @@
         <v>78</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>78</v>
@@ -8895,10 +8896,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8921,16 +8922,16 @@
         <v>78</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -8980,7 +8981,7 @@
         <v>78</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>76</v>
@@ -8998,7 +8999,7 @@
         <v>78</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>78</v>
@@ -9009,10 +9010,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9038,13 +9039,13 @@
         <v>163</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -9094,7 +9095,7 @@
         <v>78</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>76</v>
@@ -9112,7 +9113,7 @@
         <v>78</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>78</v>
@@ -9123,10 +9124,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9235,10 +9236,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9349,10 +9350,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9465,10 +9466,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9494,10 +9495,10 @@
         <v>144</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -9548,7 +9549,7 @@
         <v>78</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>76</v>
@@ -9572,15 +9573,15 @@
         <v>78</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9603,13 +9604,13 @@
         <v>78</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -9660,7 +9661,7 @@
         <v>78</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>76</v>
@@ -9678,7 +9679,7 @@
         <v>78</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>78</v>
@@ -9689,10 +9690,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9718,10 +9719,10 @@
         <v>209</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -9751,10 +9752,10 @@
         <v>110</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>78</v>
@@ -9772,7 +9773,7 @@
         <v>78</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>76</v>
@@ -9790,21 +9791,21 @@
         <v>78</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9830,10 +9831,10 @@
         <v>209</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -9863,10 +9864,10 @@
         <v>213</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>78</v>
@@ -9884,7 +9885,7 @@
         <v>78</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>76</v>
@@ -9908,15 +9909,15 @@
         <v>78</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9942,16 +9943,16 @@
         <v>209</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>78</v>
@@ -9979,10 +9980,10 @@
         <v>213</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>78</v>
@@ -10000,7 +10001,7 @@
         <v>78</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>76</v>
@@ -10018,21 +10019,21 @@
         <v>78</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10058,10 +10059,10 @@
         <v>209</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -10091,10 +10092,10 @@
         <v>110</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>78</v>
@@ -10112,7 +10113,7 @@
         <v>78</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>76</v>
@@ -10130,21 +10131,21 @@
         <v>78</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10170,10 +10171,10 @@
         <v>209</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -10203,10 +10204,10 @@
         <v>110</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>78</v>
@@ -10224,7 +10225,7 @@
         <v>78</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>76</v>
@@ -10242,21 +10243,21 @@
         <v>78</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10279,13 +10280,13 @@
         <v>78</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -10336,7 +10337,7 @@
         <v>78</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>76</v>
@@ -10354,21 +10355,21 @@
         <v>78</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10394,10 +10395,10 @@
         <v>209</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -10427,10 +10428,10 @@
         <v>213</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>78</v>
@@ -10448,7 +10449,7 @@
         <v>78</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>76</v>
@@ -10466,21 +10467,21 @@
         <v>78</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AM75" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10506,13 +10507,13 @@
         <v>163</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -10562,7 +10563,7 @@
         <v>78</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>76</v>
@@ -10580,7 +10581,7 @@
         <v>78</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>78</v>
@@ -10591,10 +10592,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10703,10 +10704,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10817,10 +10818,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -10933,10 +10934,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -10959,13 +10960,13 @@
         <v>78</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -11016,7 +11017,7 @@
         <v>78</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>86</v>
@@ -11031,24 +11032,24 @@
         <v>98</v>
       </c>
       <c r="AK80" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11074,13 +11075,13 @@
         <v>106</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -11109,10 +11110,10 @@
         <v>155</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="Z81" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>78</v>
@@ -11130,7 +11131,7 @@
         <v>78</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>76</v>
@@ -11148,7 +11149,7 @@
         <v>78</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AM81" t="s" s="2">
         <v>78</v>
@@ -11159,10 +11160,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11188,13 +11189,13 @@
         <v>209</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -11223,10 +11224,10 @@
         <v>213</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>78</v>
@@ -11244,7 +11245,7 @@
         <v>78</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>76</v>
@@ -11273,10 +11274,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11302,10 +11303,10 @@
         <v>183</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -11356,7 +11357,7 @@
         <v>78</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>76</v>
@@ -11374,7 +11375,7 @@
         <v>78</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AM83" t="s" s="2">
         <v>78</v>
@@ -11385,10 +11386,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11411,13 +11412,13 @@
         <v>78</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -11468,7 +11469,7 @@
         <v>78</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>76</v>
@@ -11483,24 +11484,24 @@
         <v>98</v>
       </c>
       <c r="AK84" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="AM84" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11523,16 +11524,16 @@
         <v>78</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -11582,7 +11583,7 @@
         <v>78</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>76</v>
@@ -11597,10 +11598,10 @@
         <v>98</v>
       </c>
       <c r="AK85" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="AM85" t="s" s="2">
         <v>78</v>

--- a/currentbuild/StructureDefinition-no-basis-encounter-auditevent.xlsx
+++ b/currentbuild/StructureDefinition-no-basis-encounter-auditevent.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.0</t>
+    <t>0.9.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-17T09:59:20+00:00</t>
+    <t>2024-04-06T16:49:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -69,7 +69,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>HL7 Norway (https://github.com/HL7Norway)</t>
   </si>
   <si>
     <t>Description</t>
